--- a/administrative_forms/011_fraudulent_activity_complaint_form--administrative_forms.xlsx
+++ b/administrative_forms/011_fraudulent_activity_complaint_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'document_1'}</t>
+          <t>document_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Document 1'}</t>
+          <t>Document 1</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'document_2'}</t>
+          <t>document_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Document 2'}</t>
+          <t>Document 2</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'document_3'}</t>
+          <t>document_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Document 3'}</t>
+          <t>Document 3</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'under_investigation'}</t>
+          <t>under_investigation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Under Investigation'}</t>
+          <t>Under Investigation</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_investigated'}</t>
+          <t>not_investigated</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Investigated'}</t>
+          <t>Not Investigated</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'credit_card_fraud'}</t>
+          <t>credit_card_fraud</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Credit Card Fraud'}</t>
+          <t>Credit Card Fraud</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'identity_theft'}</t>
+          <t>identity_theft</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Identity Theft'}</t>
+          <t>Identity Theft</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'done'}</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Done'}</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_done'}</t>
+          <t>not_done</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not Done'}</t>
+          <t>Not Done</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'dismissed'}</t>
+          <t>dismissed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Dismissed'}</t>
+          <t>Dismissed</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager_1'}</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager 1'}</t>
+          <t>Manager 1</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'manager_2'}</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Manager 2'}</t>
+          <t>Manager 2</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'manager_3'}</t>
+          <t>manager_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Manager 3'}</t>
+          <t>Manager 3</t>
         </is>
       </c>
     </row>
